--- a/sample-data/Admin_assets_2026-05-05.xlsx
+++ b/sample-data/Admin_assets_2026-05-05.xlsx
@@ -433,7 +433,7 @@
         <v>AP0001</v>
       </c>
       <c r="D2" t="str">
-        <v>2019-10-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -442,7 +442,7 @@
         <v>Allocated</v>
       </c>
       <c r="G2">
-        <v>71207</v>
+        <v>68317</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>AP0002</v>
       </c>
       <c r="D3" t="str">
-        <v>2019-04-05</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -465,7 +465,7 @@
         <v>Allocated</v>
       </c>
       <c r="G3">
-        <v>80666</v>
+        <v>84324</v>
       </c>
     </row>
     <row r="4">
@@ -473,13 +473,13 @@
         <v>AST-1003</v>
       </c>
       <c r="B4" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C4" t="str">
-        <v>AP0003</v>
+        <v>AP0002</v>
       </c>
       <c r="D4" t="str">
-        <v>2024-11-17</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -488,7 +488,7 @@
         <v>Allocated</v>
       </c>
       <c r="G4">
-        <v>104432</v>
+        <v>5583</v>
       </c>
     </row>
     <row r="5">
@@ -496,13 +496,13 @@
         <v>AST-1004</v>
       </c>
       <c r="B5" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C5" t="str">
         <v>AP0003</v>
       </c>
       <c r="D5" t="str">
-        <v>2024-11-17</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -511,7 +511,7 @@
         <v>Allocated</v>
       </c>
       <c r="G5">
-        <v>25109</v>
+        <v>82123</v>
       </c>
     </row>
     <row r="6">
@@ -519,13 +519,13 @@
         <v>AST-1005</v>
       </c>
       <c r="B6" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C6" t="str">
-        <v>AP0004</v>
+        <v>AP0003</v>
       </c>
       <c r="D6" t="str">
-        <v>2018-11-02</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -534,7 +534,7 @@
         <v>Allocated</v>
       </c>
       <c r="G6">
-        <v>45286</v>
+        <v>42154</v>
       </c>
     </row>
     <row r="7">
@@ -542,13 +542,13 @@
         <v>AST-1006</v>
       </c>
       <c r="B7" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C7" t="str">
         <v>AP0004</v>
       </c>
       <c r="D7" t="str">
-        <v>2018-11-02</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -557,7 +557,7 @@
         <v>Allocated</v>
       </c>
       <c r="G7">
-        <v>14597</v>
+        <v>98435</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>AST-1007</v>
       </c>
       <c r="B8" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C8" t="str">
-        <v>AP0005</v>
+        <v>AP0004</v>
       </c>
       <c r="D8" t="str">
-        <v>2023-10-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -580,7 +580,7 @@
         <v>Allocated</v>
       </c>
       <c r="G8">
-        <v>95990</v>
+        <v>38756</v>
       </c>
     </row>
     <row r="9">
@@ -591,10 +591,10 @@
         <v>Laptop</v>
       </c>
       <c r="C9" t="str">
-        <v>AP0006</v>
+        <v>AP0005</v>
       </c>
       <c r="D9" t="str">
-        <v>2023-02-06</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -603,7 +603,7 @@
         <v>Allocated</v>
       </c>
       <c r="G9">
-        <v>79995</v>
+        <v>74861</v>
       </c>
     </row>
     <row r="10">
@@ -611,13 +611,13 @@
         <v>AST-1009</v>
       </c>
       <c r="B10" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C10" t="str">
-        <v>AP0007</v>
+        <v>AP0005</v>
       </c>
       <c r="D10" t="str">
-        <v>2020-03-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v>Allocated</v>
       </c>
       <c r="G10">
-        <v>59790</v>
+        <v>50043</v>
       </c>
     </row>
     <row r="11">
@@ -637,10 +637,10 @@
         <v>Laptop</v>
       </c>
       <c r="C11" t="str">
-        <v>AP0008</v>
+        <v>AP0006</v>
       </c>
       <c r="D11" t="str">
-        <v>2017-01-05</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -649,7 +649,7 @@
         <v>Allocated</v>
       </c>
       <c r="G11">
-        <v>79056</v>
+        <v>94068</v>
       </c>
     </row>
     <row r="12">
@@ -657,13 +657,13 @@
         <v>AST-1011</v>
       </c>
       <c r="B12" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C12" t="str">
-        <v>AP0008</v>
+        <v>AP0007</v>
       </c>
       <c r="D12" t="str">
-        <v>2017-01-05</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -672,7 +672,7 @@
         <v>Allocated</v>
       </c>
       <c r="G12">
-        <v>56667</v>
+        <v>79638</v>
       </c>
     </row>
     <row r="13">
@@ -680,13 +680,13 @@
         <v>AST-1012</v>
       </c>
       <c r="B13" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C13" t="str">
-        <v>AP0009</v>
+        <v>AP0007</v>
       </c>
       <c r="D13" t="str">
-        <v>2017-06-10</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -695,7 +695,7 @@
         <v>Allocated</v>
       </c>
       <c r="G13">
-        <v>64410</v>
+        <v>11346</v>
       </c>
     </row>
     <row r="14">
@@ -703,7 +703,7 @@
         <v>AST-1013</v>
       </c>
       <c r="B14" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C14" t="str">
         <v>AP0009</v>
@@ -718,7 +718,7 @@
         <v>Allocated</v>
       </c>
       <c r="G14">
-        <v>40813</v>
+        <v>49558</v>
       </c>
     </row>
     <row r="15">
@@ -726,13 +726,13 @@
         <v>AST-1014</v>
       </c>
       <c r="B15" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C15" t="str">
-        <v>AP0010</v>
+        <v>AP0009</v>
       </c>
       <c r="D15" t="str">
-        <v>2020-11-18</v>
+        <v>2017-06-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -741,7 +741,7 @@
         <v>Allocated</v>
       </c>
       <c r="G15">
-        <v>70879</v>
+        <v>52136</v>
       </c>
     </row>
     <row r="16">
@@ -752,10 +752,10 @@
         <v>Laptop</v>
       </c>
       <c r="C16" t="str">
-        <v>AP0012</v>
+        <v>AP0010</v>
       </c>
       <c r="D16" t="str">
-        <v>2017-07-27</v>
+        <v>2020-11-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -764,7 +764,7 @@
         <v>Allocated</v>
       </c>
       <c r="G16">
-        <v>91010</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="17">
@@ -772,7 +772,7 @@
         <v>AST-1016</v>
       </c>
       <c r="B17" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C17" t="str">
         <v>AP0012</v>
@@ -787,7 +787,7 @@
         <v>Allocated</v>
       </c>
       <c r="G17">
-        <v>45884</v>
+        <v>82162</v>
       </c>
     </row>
     <row r="18">
@@ -795,13 +795,13 @@
         <v>AST-1017</v>
       </c>
       <c r="B18" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C18" t="str">
-        <v>AP0013</v>
+        <v>AP0012</v>
       </c>
       <c r="D18" t="str">
-        <v>2024-04-02</v>
+        <v>2017-07-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -810,7 +810,7 @@
         <v>Allocated</v>
       </c>
       <c r="G18">
-        <v>76305</v>
+        <v>22234</v>
       </c>
     </row>
     <row r="19">
@@ -818,13 +818,13 @@
         <v>AST-1018</v>
       </c>
       <c r="B19" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C19" t="str">
-        <v>AP0013</v>
+        <v>AP0014</v>
       </c>
       <c r="D19" t="str">
-        <v>2024-04-02</v>
+        <v>2024-03-22</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -833,7 +833,7 @@
         <v>Allocated</v>
       </c>
       <c r="G19">
-        <v>56796</v>
+        <v>75895</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +841,7 @@
         <v>AST-1019</v>
       </c>
       <c r="B20" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C20" t="str">
         <v>AP0014</v>
@@ -856,7 +856,7 @@
         <v>Allocated</v>
       </c>
       <c r="G20">
-        <v>58029</v>
+        <v>53903</v>
       </c>
     </row>
     <row r="21">
@@ -864,13 +864,13 @@
         <v>AST-1020</v>
       </c>
       <c r="B21" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C21" t="str">
-        <v>AP0014</v>
+        <v>AP0015</v>
       </c>
       <c r="D21" t="str">
-        <v>2024-03-22</v>
+        <v>2022-05-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -879,7 +879,7 @@
         <v>Allocated</v>
       </c>
       <c r="G21">
-        <v>3335</v>
+        <v>90608</v>
       </c>
     </row>
     <row r="22">
@@ -890,10 +890,10 @@
         <v>Laptop</v>
       </c>
       <c r="C22" t="str">
-        <v>AP0015</v>
+        <v>AP0016</v>
       </c>
       <c r="D22" t="str">
-        <v>2022-05-03</v>
+        <v>2021-06-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -902,7 +902,7 @@
         <v>Allocated</v>
       </c>
       <c r="G22">
-        <v>86581</v>
+        <v>102499</v>
       </c>
     </row>
     <row r="23">
@@ -913,10 +913,10 @@
         <v>Laptop</v>
       </c>
       <c r="C23" t="str">
-        <v>AP0016</v>
+        <v>AP0017</v>
       </c>
       <c r="D23" t="str">
-        <v>2021-06-18</v>
+        <v>2017-08-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -925,7 +925,7 @@
         <v>Allocated</v>
       </c>
       <c r="G23">
-        <v>81964</v>
+        <v>105657</v>
       </c>
     </row>
     <row r="24">
@@ -933,13 +933,13 @@
         <v>AST-1023</v>
       </c>
       <c r="B24" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C24" t="str">
-        <v>AP0016</v>
+        <v>AP0018</v>
       </c>
       <c r="D24" t="str">
-        <v>2021-06-18</v>
+        <v>2020-10-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v>Allocated</v>
       </c>
       <c r="G24">
-        <v>59103</v>
+        <v>75672</v>
       </c>
     </row>
     <row r="25">
@@ -959,10 +959,10 @@
         <v>Laptop</v>
       </c>
       <c r="C25" t="str">
-        <v>AP0017</v>
+        <v>AP0019</v>
       </c>
       <c r="D25" t="str">
-        <v>2017-08-28</v>
+        <v>2021-01-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Allocated</v>
       </c>
       <c r="G25">
-        <v>97874</v>
+        <v>73055</v>
       </c>
     </row>
     <row r="26">
@@ -982,10 +982,10 @@
         <v>Laptop</v>
       </c>
       <c r="C26" t="str">
-        <v>AP0018</v>
+        <v>AP0021</v>
       </c>
       <c r="D26" t="str">
-        <v>2020-10-17</v>
+        <v>2023-02-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -994,7 +994,7 @@
         <v>Allocated</v>
       </c>
       <c r="G26">
-        <v>65683</v>
+        <v>105149</v>
       </c>
     </row>
     <row r="27">
@@ -1002,13 +1002,13 @@
         <v>AST-1026</v>
       </c>
       <c r="B27" t="str">
-        <v>SIM</v>
+        <v>Access Card</v>
       </c>
       <c r="C27" t="str">
-        <v>AP0018</v>
+        <v>AP0021</v>
       </c>
       <c r="D27" t="str">
-        <v>2020-10-17</v>
+        <v>2023-02-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1017,7 +1017,7 @@
         <v>Allocated</v>
       </c>
       <c r="G27">
-        <v>23495</v>
+        <v>55584</v>
       </c>
     </row>
     <row r="28">
@@ -1028,10 +1028,10 @@
         <v>Laptop</v>
       </c>
       <c r="C28" t="str">
-        <v>AP0019</v>
+        <v>AP0023</v>
       </c>
       <c r="D28" t="str">
-        <v>2021-01-03</v>
+        <v>2020-07-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1040,7 +1040,7 @@
         <v>Allocated</v>
       </c>
       <c r="G28">
-        <v>50589</v>
+        <v>60055</v>
       </c>
     </row>
     <row r="29">
@@ -1048,13 +1048,13 @@
         <v>AST-1028</v>
       </c>
       <c r="B29" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C29" t="str">
-        <v>AP0021</v>
+        <v>AP0023</v>
       </c>
       <c r="D29" t="str">
-        <v>2023-02-04</v>
+        <v>2020-07-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1063,7 +1063,7 @@
         <v>Allocated</v>
       </c>
       <c r="G29">
-        <v>70626</v>
+        <v>13165</v>
       </c>
     </row>
     <row r="30">
@@ -1071,13 +1071,13 @@
         <v>AST-1029</v>
       </c>
       <c r="B30" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C30" t="str">
-        <v>AP0021</v>
+        <v>AP0024</v>
       </c>
       <c r="D30" t="str">
-        <v>2023-02-04</v>
+        <v>2022-04-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1086,7 +1086,7 @@
         <v>Allocated</v>
       </c>
       <c r="G30">
-        <v>12631</v>
+        <v>97930</v>
       </c>
     </row>
     <row r="31">
@@ -1094,13 +1094,13 @@
         <v>AST-1030</v>
       </c>
       <c r="B31" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C31" t="str">
-        <v>AP0022</v>
+        <v>AP0024</v>
       </c>
       <c r="D31" t="str">
-        <v>2019-08-06</v>
+        <v>2022-04-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1109,7 +1109,7 @@
         <v>Allocated</v>
       </c>
       <c r="G31">
-        <v>95071</v>
+        <v>58134</v>
       </c>
     </row>
     <row r="32">
@@ -1117,13 +1117,13 @@
         <v>AST-1031</v>
       </c>
       <c r="B32" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C32" t="str">
-        <v>AP0022</v>
+        <v>AP0025</v>
       </c>
       <c r="D32" t="str">
-        <v>2019-08-06</v>
+        <v>2023-01-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v>Allocated</v>
       </c>
       <c r="G32">
-        <v>31758</v>
+        <v>108060</v>
       </c>
     </row>
     <row r="33">
@@ -1143,10 +1143,10 @@
         <v>Laptop</v>
       </c>
       <c r="C33" t="str">
-        <v>AP0023</v>
+        <v>AP0026</v>
       </c>
       <c r="D33" t="str">
-        <v>2020-07-26</v>
+        <v>2024-10-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1155,7 +1155,7 @@
         <v>Allocated</v>
       </c>
       <c r="G33">
-        <v>88026</v>
+        <v>102873</v>
       </c>
     </row>
     <row r="34">
@@ -1163,13 +1163,13 @@
         <v>AST-1033</v>
       </c>
       <c r="B34" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C34" t="str">
-        <v>AP0023</v>
+        <v>AP0027</v>
       </c>
       <c r="D34" t="str">
-        <v>2020-07-26</v>
+        <v>2018-10-05</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1178,7 +1178,7 @@
         <v>Allocated</v>
       </c>
       <c r="G34">
-        <v>14516</v>
+        <v>69168</v>
       </c>
     </row>
     <row r="35">
@@ -1189,10 +1189,10 @@
         <v>Laptop</v>
       </c>
       <c r="C35" t="str">
-        <v>AP0024</v>
+        <v>AP0028</v>
       </c>
       <c r="D35" t="str">
-        <v>2022-04-28</v>
+        <v>2022-05-14</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1201,7 +1201,7 @@
         <v>Allocated</v>
       </c>
       <c r="G35">
-        <v>66975</v>
+        <v>61935</v>
       </c>
     </row>
     <row r="36">
@@ -1212,10 +1212,10 @@
         <v>Laptop</v>
       </c>
       <c r="C36" t="str">
-        <v>AP0025</v>
+        <v>AP0029</v>
       </c>
       <c r="D36" t="str">
-        <v>2023-01-24</v>
+        <v>2019-11-01</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1224,7 +1224,7 @@
         <v>Allocated</v>
       </c>
       <c r="G36">
-        <v>79601</v>
+        <v>81557</v>
       </c>
     </row>
     <row r="37">
@@ -1235,10 +1235,10 @@
         <v>Access Card</v>
       </c>
       <c r="C37" t="str">
-        <v>AP0025</v>
+        <v>AP0029</v>
       </c>
       <c r="D37" t="str">
-        <v>2023-01-24</v>
+        <v>2019-11-01</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1247,7 +1247,7 @@
         <v>Allocated</v>
       </c>
       <c r="G37">
-        <v>59394</v>
+        <v>14648</v>
       </c>
     </row>
     <row r="38">
@@ -1258,10 +1258,10 @@
         <v>Laptop</v>
       </c>
       <c r="C38" t="str">
-        <v>AP0026</v>
+        <v>AP0030</v>
       </c>
       <c r="D38" t="str">
-        <v>2024-10-21</v>
+        <v>2020-10-12</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1270,7 +1270,7 @@
         <v>Allocated</v>
       </c>
       <c r="G38">
-        <v>100941</v>
+        <v>108431</v>
       </c>
     </row>
     <row r="39">
@@ -1281,10 +1281,10 @@
         <v>Laptop</v>
       </c>
       <c r="C39" t="str">
-        <v>AP0027</v>
+        <v>AP0031</v>
       </c>
       <c r="D39" t="str">
-        <v>2018-10-05</v>
+        <v>2017-04-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1293,7 +1293,7 @@
         <v>Allocated</v>
       </c>
       <c r="G39">
-        <v>61326</v>
+        <v>71178</v>
       </c>
     </row>
     <row r="40">
@@ -1304,10 +1304,10 @@
         <v>Laptop</v>
       </c>
       <c r="C40" t="str">
-        <v>AP0028</v>
+        <v>AP0033</v>
       </c>
       <c r="D40" t="str">
-        <v>2022-05-14</v>
+        <v>2024-11-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>Allocated</v>
       </c>
       <c r="G40">
-        <v>63692</v>
+        <v>52066</v>
       </c>
     </row>
     <row r="41">
@@ -1327,10 +1327,10 @@
         <v>Phone</v>
       </c>
       <c r="C41" t="str">
-        <v>AP0028</v>
+        <v>AP0033</v>
       </c>
       <c r="D41" t="str">
-        <v>2022-05-14</v>
+        <v>2024-11-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1339,7 +1339,7 @@
         <v>Allocated</v>
       </c>
       <c r="G41">
-        <v>53269</v>
+        <v>52961</v>
       </c>
     </row>
     <row r="42">
@@ -1350,10 +1350,10 @@
         <v>Laptop</v>
       </c>
       <c r="C42" t="str">
-        <v>AP0029</v>
+        <v>AP0034</v>
       </c>
       <c r="D42" t="str">
-        <v>2019-11-01</v>
+        <v>2021-02-05</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>Allocated</v>
       </c>
       <c r="G42">
-        <v>107367</v>
+        <v>73529</v>
       </c>
     </row>
     <row r="43">
@@ -1370,13 +1370,13 @@
         <v>AST-1042</v>
       </c>
       <c r="B43" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C43" t="str">
-        <v>AP0029</v>
+        <v>AP0035</v>
       </c>
       <c r="D43" t="str">
-        <v>2019-11-01</v>
+        <v>2021-07-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1385,7 +1385,7 @@
         <v>Allocated</v>
       </c>
       <c r="G43">
-        <v>42085</v>
+        <v>75546</v>
       </c>
     </row>
     <row r="44">
@@ -1396,10 +1396,10 @@
         <v>Laptop</v>
       </c>
       <c r="C44" t="str">
-        <v>AP0031</v>
+        <v>AP0036</v>
       </c>
       <c r="D44" t="str">
-        <v>2017-04-27</v>
+        <v>2019-11-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>Allocated</v>
       </c>
       <c r="G44">
-        <v>47388</v>
+        <v>88148</v>
       </c>
     </row>
     <row r="45">
@@ -1416,13 +1416,13 @@
         <v>AST-1044</v>
       </c>
       <c r="B45" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C45" t="str">
-        <v>AP0033</v>
+        <v>AP0036</v>
       </c>
       <c r="D45" t="str">
-        <v>2024-11-21</v>
+        <v>2019-11-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1431,7 +1431,7 @@
         <v>Allocated</v>
       </c>
       <c r="G45">
-        <v>92849</v>
+        <v>33385</v>
       </c>
     </row>
     <row r="46">
@@ -1442,10 +1442,10 @@
         <v>Laptop</v>
       </c>
       <c r="C46" t="str">
-        <v>AP0034</v>
+        <v>AP0038</v>
       </c>
       <c r="D46" t="str">
-        <v>2021-02-05</v>
+        <v>2018-02-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1454,7 +1454,7 @@
         <v>Allocated</v>
       </c>
       <c r="G46">
-        <v>109393</v>
+        <v>54726</v>
       </c>
     </row>
     <row r="47">
@@ -1462,13 +1462,13 @@
         <v>AST-1046</v>
       </c>
       <c r="B47" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C47" t="str">
-        <v>AP0034</v>
+        <v>AP0039</v>
       </c>
       <c r="D47" t="str">
-        <v>2021-02-05</v>
+        <v>2017-05-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1477,7 +1477,7 @@
         <v>Allocated</v>
       </c>
       <c r="G47">
-        <v>31585</v>
+        <v>59034</v>
       </c>
     </row>
     <row r="48">
@@ -1485,13 +1485,13 @@
         <v>AST-1047</v>
       </c>
       <c r="B48" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C48" t="str">
-        <v>AP0035</v>
+        <v>AP0039</v>
       </c>
       <c r="D48" t="str">
-        <v>2021-07-24</v>
+        <v>2017-05-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1500,7 +1500,7 @@
         <v>Allocated</v>
       </c>
       <c r="G48">
-        <v>55431</v>
+        <v>55462</v>
       </c>
     </row>
     <row r="49">
@@ -1511,10 +1511,10 @@
         <v>Laptop</v>
       </c>
       <c r="C49" t="str">
-        <v>AP0036</v>
+        <v>AP0040</v>
       </c>
       <c r="D49" t="str">
-        <v>2019-11-23</v>
+        <v>2022-01-15</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1523,7 +1523,7 @@
         <v>Allocated</v>
       </c>
       <c r="G49">
-        <v>77305</v>
+        <v>105090</v>
       </c>
     </row>
     <row r="50">
@@ -1531,13 +1531,13 @@
         <v>AST-1049</v>
       </c>
       <c r="B50" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C50" t="str">
-        <v>AP0038</v>
+        <v>AP0040</v>
       </c>
       <c r="D50" t="str">
-        <v>2018-02-10</v>
+        <v>2022-01-15</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1546,7 +1546,7 @@
         <v>Allocated</v>
       </c>
       <c r="G50">
-        <v>79803</v>
+        <v>33712</v>
       </c>
     </row>
     <row r="51">
@@ -1554,13 +1554,13 @@
         <v>AST-1050</v>
       </c>
       <c r="B51" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C51" t="str">
-        <v>AP0038</v>
+        <v>AP0041</v>
       </c>
       <c r="D51" t="str">
-        <v>2018-02-10</v>
+        <v>2017-11-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1569,7 +1569,7 @@
         <v>Allocated</v>
       </c>
       <c r="G51">
-        <v>49846</v>
+        <v>60066</v>
       </c>
     </row>
     <row r="52">
@@ -1577,13 +1577,13 @@
         <v>AST-1051</v>
       </c>
       <c r="B52" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C52" t="str">
-        <v>AP0039</v>
+        <v>AP0041</v>
       </c>
       <c r="D52" t="str">
-        <v>2017-05-17</v>
+        <v>2017-11-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1592,7 +1592,7 @@
         <v>Allocated</v>
       </c>
       <c r="G52">
-        <v>105528</v>
+        <v>43809</v>
       </c>
     </row>
     <row r="53">
@@ -1600,13 +1600,13 @@
         <v>AST-1052</v>
       </c>
       <c r="B53" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C53" t="str">
-        <v>AP0039</v>
+        <v>AP0042</v>
       </c>
       <c r="D53" t="str">
-        <v>2017-05-17</v>
+        <v>2020-12-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1615,7 +1615,7 @@
         <v>Allocated</v>
       </c>
       <c r="G53">
-        <v>19875</v>
+        <v>68532</v>
       </c>
     </row>
     <row r="54">
@@ -1626,10 +1626,10 @@
         <v>Laptop</v>
       </c>
       <c r="C54" t="str">
-        <v>AP0040</v>
+        <v>AP0043</v>
       </c>
       <c r="D54" t="str">
-        <v>2022-01-15</v>
+        <v>2023-08-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -1638,7 +1638,7 @@
         <v>Allocated</v>
       </c>
       <c r="G54">
-        <v>73808</v>
+        <v>101674</v>
       </c>
     </row>
     <row r="55">
@@ -1649,10 +1649,10 @@
         <v>Access Card</v>
       </c>
       <c r="C55" t="str">
-        <v>AP0040</v>
+        <v>AP0043</v>
       </c>
       <c r="D55" t="str">
-        <v>2022-01-15</v>
+        <v>2023-08-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>Allocated</v>
       </c>
       <c r="G55">
-        <v>16275</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="56">
@@ -1672,10 +1672,10 @@
         <v>Laptop</v>
       </c>
       <c r="C56" t="str">
-        <v>AP0041</v>
+        <v>AP0045</v>
       </c>
       <c r="D56" t="str">
-        <v>2017-11-17</v>
+        <v>2022-06-07</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1684,7 +1684,7 @@
         <v>Allocated</v>
       </c>
       <c r="G56">
-        <v>49020</v>
+        <v>93658</v>
       </c>
     </row>
     <row r="57">
@@ -1695,10 +1695,10 @@
         <v>Laptop</v>
       </c>
       <c r="C57" t="str">
-        <v>AP0042</v>
+        <v>AP0046</v>
       </c>
       <c r="D57" t="str">
-        <v>2020-12-24</v>
+        <v>2017-04-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1707,7 +1707,7 @@
         <v>Allocated</v>
       </c>
       <c r="G57">
-        <v>100471</v>
+        <v>75028</v>
       </c>
     </row>
     <row r="58">
@@ -1718,10 +1718,10 @@
         <v>Laptop</v>
       </c>
       <c r="C58" t="str">
-        <v>AP0043</v>
+        <v>AP0047</v>
       </c>
       <c r="D58" t="str">
-        <v>2023-08-21</v>
+        <v>2019-09-08</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -1730,7 +1730,7 @@
         <v>Allocated</v>
       </c>
       <c r="G58">
-        <v>52611</v>
+        <v>108341</v>
       </c>
     </row>
     <row r="59">
@@ -1741,10 +1741,10 @@
         <v>Laptop</v>
       </c>
       <c r="C59" t="str">
-        <v>AP0045</v>
+        <v>AP0048</v>
       </c>
       <c r="D59" t="str">
-        <v>2022-06-07</v>
+        <v>2020-02-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v>Allocated</v>
       </c>
       <c r="G59">
-        <v>64627</v>
+        <v>97874</v>
       </c>
     </row>
     <row r="60">
@@ -1761,13 +1761,13 @@
         <v>AST-1059</v>
       </c>
       <c r="B60" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C60" t="str">
-        <v>AP0045</v>
+        <v>AP0050</v>
       </c>
       <c r="D60" t="str">
-        <v>2022-06-07</v>
+        <v>2017-04-08</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>Allocated</v>
       </c>
       <c r="G60">
-        <v>3701</v>
+        <v>65683</v>
       </c>
     </row>
     <row r="61">
@@ -1784,13 +1784,13 @@
         <v>AST-1060</v>
       </c>
       <c r="B61" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C61" t="str">
-        <v>AP0046</v>
+        <v>AP0050</v>
       </c>
       <c r="D61" t="str">
-        <v>2017-04-17</v>
+        <v>2017-04-08</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -1799,7 +1799,7 @@
         <v>Allocated</v>
       </c>
       <c r="G61">
-        <v>86515</v>
+        <v>23495</v>
       </c>
     </row>
     <row r="62">
@@ -1810,10 +1810,10 @@
         <v>Laptop</v>
       </c>
       <c r="C62" t="str">
-        <v>AP0047</v>
+        <v>AP0051</v>
       </c>
       <c r="D62" t="str">
-        <v>2019-09-08</v>
+        <v>2024-06-08</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -1822,7 +1822,7 @@
         <v>Allocated</v>
       </c>
       <c r="G62">
-        <v>53352</v>
+        <v>50589</v>
       </c>
     </row>
     <row r="63">
@@ -1830,13 +1830,13 @@
         <v>AST-1062</v>
       </c>
       <c r="B63" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C63" t="str">
-        <v>AP0047</v>
+        <v>AP0052</v>
       </c>
       <c r="D63" t="str">
-        <v>2019-09-08</v>
+        <v>2020-09-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Allocated</v>
       </c>
       <c r="G63">
-        <v>19791</v>
+        <v>70626</v>
       </c>
     </row>
     <row r="64">
@@ -1853,13 +1853,13 @@
         <v>AST-1063</v>
       </c>
       <c r="B64" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C64" t="str">
-        <v>AP0048</v>
+        <v>AP0052</v>
       </c>
       <c r="D64" t="str">
-        <v>2020-02-21</v>
+        <v>2020-09-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1868,7 +1868,7 @@
         <v>Allocated</v>
       </c>
       <c r="G64">
-        <v>69702</v>
+        <v>12631</v>
       </c>
     </row>
     <row r="65">
@@ -1879,10 +1879,10 @@
         <v>Laptop</v>
       </c>
       <c r="C65" t="str">
-        <v>AP0050</v>
+        <v>AP0053</v>
       </c>
       <c r="D65" t="str">
-        <v>2017-04-08</v>
+        <v>2022-10-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -1891,7 +1891,7 @@
         <v>Allocated</v>
       </c>
       <c r="G65">
-        <v>46902</v>
+        <v>95071</v>
       </c>
     </row>
     <row r="66">
@@ -1899,13 +1899,13 @@
         <v>AST-1065</v>
       </c>
       <c r="B66" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C66" t="str">
-        <v>AP0051</v>
+        <v>AP0053</v>
       </c>
       <c r="D66" t="str">
-        <v>2024-06-08</v>
+        <v>2022-10-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -1914,7 +1914,7 @@
         <v>Allocated</v>
       </c>
       <c r="G66">
-        <v>105452</v>
+        <v>31758</v>
       </c>
     </row>
     <row r="67">
@@ -1922,13 +1922,13 @@
         <v>AST-1066</v>
       </c>
       <c r="B67" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C67" t="str">
-        <v>AP0051</v>
+        <v>AP0054</v>
       </c>
       <c r="D67" t="str">
-        <v>2024-06-08</v>
+        <v>2017-04-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -1937,7 +1937,7 @@
         <v>Allocated</v>
       </c>
       <c r="G67">
-        <v>45607</v>
+        <v>88026</v>
       </c>
     </row>
     <row r="68">
@@ -1945,13 +1945,13 @@
         <v>AST-1067</v>
       </c>
       <c r="B68" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C68" t="str">
-        <v>AP0052</v>
+        <v>AP0054</v>
       </c>
       <c r="D68" t="str">
-        <v>2020-09-23</v>
+        <v>2017-04-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -1960,7 +1960,7 @@
         <v>Allocated</v>
       </c>
       <c r="G68">
-        <v>103572</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="69">
@@ -1971,10 +1971,10 @@
         <v>Laptop</v>
       </c>
       <c r="C69" t="str">
-        <v>AP0053</v>
+        <v>AP0055</v>
       </c>
       <c r="D69" t="str">
-        <v>2022-10-21</v>
+        <v>2017-01-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -1983,7 +1983,7 @@
         <v>Allocated</v>
       </c>
       <c r="G69">
-        <v>98525</v>
+        <v>66975</v>
       </c>
     </row>
     <row r="70">
@@ -1994,10 +1994,10 @@
         <v>Laptop</v>
       </c>
       <c r="C70" t="str">
-        <v>AP0054</v>
+        <v>AP0056</v>
       </c>
       <c r="D70" t="str">
-        <v>2017-04-18</v>
+        <v>2022-08-06</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -2006,7 +2006,7 @@
         <v>Allocated</v>
       </c>
       <c r="G70">
-        <v>106492</v>
+        <v>79601</v>
       </c>
     </row>
     <row r="71">
@@ -2014,13 +2014,13 @@
         <v>AST-1070</v>
       </c>
       <c r="B71" t="str">
-        <v>Phone</v>
+        <v>Access Card</v>
       </c>
       <c r="C71" t="str">
-        <v>AP0054</v>
+        <v>AP0056</v>
       </c>
       <c r="D71" t="str">
-        <v>2017-04-18</v>
+        <v>2022-08-06</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -2029,7 +2029,7 @@
         <v>Allocated</v>
       </c>
       <c r="G71">
-        <v>37856</v>
+        <v>59394</v>
       </c>
     </row>
     <row r="72">
@@ -2040,10 +2040,10 @@
         <v>Laptop</v>
       </c>
       <c r="C72" t="str">
-        <v>AP0055</v>
+        <v>AP0057</v>
       </c>
       <c r="D72" t="str">
-        <v>2017-01-19</v>
+        <v>2024-11-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -2052,7 +2052,7 @@
         <v>Allocated</v>
       </c>
       <c r="G72">
-        <v>95288</v>
+        <v>100941</v>
       </c>
     </row>
     <row r="73">
@@ -2063,10 +2063,10 @@
         <v>Laptop</v>
       </c>
       <c r="C73" t="str">
-        <v>AP0056</v>
+        <v>AP0058</v>
       </c>
       <c r="D73" t="str">
-        <v>2022-08-06</v>
+        <v>2021-07-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -2075,7 +2075,7 @@
         <v>Allocated</v>
       </c>
       <c r="G73">
-        <v>55281</v>
+        <v>61326</v>
       </c>
     </row>
     <row r="74">
@@ -2083,13 +2083,13 @@
         <v>AST-1073</v>
       </c>
       <c r="B74" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C74" t="str">
-        <v>AP0056</v>
+        <v>AP0059</v>
       </c>
       <c r="D74" t="str">
-        <v>2022-08-06</v>
+        <v>2019-02-14</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
         <v>Allocated</v>
       </c>
       <c r="G74">
-        <v>7832</v>
+        <v>63692</v>
       </c>
     </row>
     <row r="75">
@@ -2106,13 +2106,13 @@
         <v>AST-1074</v>
       </c>
       <c r="B75" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C75" t="str">
-        <v>AP0057</v>
+        <v>AP0059</v>
       </c>
       <c r="D75" t="str">
-        <v>2024-11-21</v>
+        <v>2019-02-14</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -2121,7 +2121,7 @@
         <v>Allocated</v>
       </c>
       <c r="G75">
-        <v>60178</v>
+        <v>53269</v>
       </c>
     </row>
     <row r="76">
@@ -2129,13 +2129,13 @@
         <v>AST-1075</v>
       </c>
       <c r="B76" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C76" t="str">
-        <v>AP0057</v>
+        <v>AP0060</v>
       </c>
       <c r="D76" t="str">
-        <v>2024-11-21</v>
+        <v>2023-12-14</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -2144,7 +2144,7 @@
         <v>Allocated</v>
       </c>
       <c r="G76">
-        <v>56382</v>
+        <v>107367</v>
       </c>
     </row>
     <row r="77">
@@ -2152,13 +2152,13 @@
         <v>AST-1076</v>
       </c>
       <c r="B77" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C77" t="str">
-        <v>AP0058</v>
+        <v>AP0060</v>
       </c>
       <c r="D77" t="str">
-        <v>2021-07-21</v>
+        <v>2023-12-14</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -2167,7 +2167,7 @@
         <v>Allocated</v>
       </c>
       <c r="G77">
-        <v>53392</v>
+        <v>42085</v>
       </c>
     </row>
     <row r="78">
@@ -2178,10 +2178,10 @@
         <v>Laptop</v>
       </c>
       <c r="C78" t="str">
-        <v>AP0059</v>
+        <v>AP0062</v>
       </c>
       <c r="D78" t="str">
-        <v>2019-02-14</v>
+        <v>2021-03-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -2190,7 +2190,7 @@
         <v>Allocated</v>
       </c>
       <c r="G78">
-        <v>61022</v>
+        <v>47388</v>
       </c>
     </row>
     <row r="79">
@@ -2198,13 +2198,13 @@
         <v>AST-1078</v>
       </c>
       <c r="B79" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C79" t="str">
-        <v>AP0059</v>
+        <v>AP0064</v>
       </c>
       <c r="D79" t="str">
-        <v>2019-02-14</v>
+        <v>2022-04-12</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -2213,7 +2213,7 @@
         <v>Allocated</v>
       </c>
       <c r="G79">
-        <v>14881</v>
+        <v>92849</v>
       </c>
     </row>
     <row r="80">
@@ -2224,10 +2224,10 @@
         <v>Laptop</v>
       </c>
       <c r="C80" t="str">
-        <v>AP0060</v>
+        <v>AP0065</v>
       </c>
       <c r="D80" t="str">
-        <v>2023-12-14</v>
+        <v>2017-04-14</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -2236,7 +2236,7 @@
         <v>Allocated</v>
       </c>
       <c r="G80">
-        <v>106698</v>
+        <v>109393</v>
       </c>
     </row>
     <row r="81">
@@ -2244,13 +2244,13 @@
         <v>AST-1080</v>
       </c>
       <c r="B81" t="str">
-        <v>Access Card</v>
+        <v>Phone</v>
       </c>
       <c r="C81" t="str">
-        <v>AP0060</v>
+        <v>AP0065</v>
       </c>
       <c r="D81" t="str">
-        <v>2023-12-14</v>
+        <v>2017-04-14</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -2259,7 +2259,7 @@
         <v>Allocated</v>
       </c>
       <c r="G81">
-        <v>51043</v>
+        <v>31585</v>
       </c>
     </row>
     <row r="82">
@@ -2270,10 +2270,10 @@
         <v>Laptop</v>
       </c>
       <c r="C82" t="str">
-        <v>AP0061</v>
+        <v>AP0066</v>
       </c>
       <c r="D82" t="str">
-        <v>2022-07-03</v>
+        <v>2020-05-04</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -2282,7 +2282,7 @@
         <v>Allocated</v>
       </c>
       <c r="G82">
-        <v>47232</v>
+        <v>55431</v>
       </c>
     </row>
     <row r="83">
@@ -2290,13 +2290,13 @@
         <v>AST-1082</v>
       </c>
       <c r="B83" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C83" t="str">
-        <v>AP0061</v>
+        <v>AP0067</v>
       </c>
       <c r="D83" t="str">
-        <v>2022-07-03</v>
+        <v>2024-12-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -2305,7 +2305,7 @@
         <v>Allocated</v>
       </c>
       <c r="G83">
-        <v>26802</v>
+        <v>77305</v>
       </c>
     </row>
     <row r="84">
@@ -2316,10 +2316,10 @@
         <v>Laptop</v>
       </c>
       <c r="C84" t="str">
-        <v>AP0062</v>
+        <v>AP0068</v>
       </c>
       <c r="D84" t="str">
-        <v>2021-03-10</v>
+        <v>2023-07-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -2328,7 +2328,7 @@
         <v>Allocated</v>
       </c>
       <c r="G84">
-        <v>64087</v>
+        <v>79803</v>
       </c>
     </row>
     <row r="85">
@@ -2339,10 +2339,10 @@
         <v>SIM</v>
       </c>
       <c r="C85" t="str">
-        <v>AP0062</v>
+        <v>AP0068</v>
       </c>
       <c r="D85" t="str">
-        <v>2021-03-10</v>
+        <v>2023-07-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -2351,7 +2351,7 @@
         <v>Allocated</v>
       </c>
       <c r="G85">
-        <v>53865</v>
+        <v>49846</v>
       </c>
     </row>
     <row r="86">
@@ -2362,10 +2362,10 @@
         <v>Laptop</v>
       </c>
       <c r="C86" t="str">
-        <v>AP0064</v>
+        <v>AP0069</v>
       </c>
       <c r="D86" t="str">
-        <v>2022-04-12</v>
+        <v>2018-02-07</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -2374,7 +2374,7 @@
         <v>Allocated</v>
       </c>
       <c r="G86">
-        <v>99889</v>
+        <v>105528</v>
       </c>
     </row>
     <row r="87">
@@ -2385,10 +2385,10 @@
         <v>Phone</v>
       </c>
       <c r="C87" t="str">
-        <v>AP0064</v>
+        <v>AP0069</v>
       </c>
       <c r="D87" t="str">
-        <v>2022-04-12</v>
+        <v>2018-02-07</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -2397,7 +2397,7 @@
         <v>Allocated</v>
       </c>
       <c r="G87">
-        <v>14101</v>
+        <v>19875</v>
       </c>
     </row>
     <row r="88">
@@ -2408,10 +2408,10 @@
         <v>Laptop</v>
       </c>
       <c r="C88" t="str">
-        <v>AP0065</v>
+        <v>AP0070</v>
       </c>
       <c r="D88" t="str">
-        <v>2017-04-14</v>
+        <v>2018-12-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -2420,7 +2420,7 @@
         <v>Allocated</v>
       </c>
       <c r="G88">
-        <v>101879</v>
+        <v>73808</v>
       </c>
     </row>
     <row r="89">
@@ -2428,13 +2428,13 @@
         <v>AST-1088</v>
       </c>
       <c r="B89" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C89" t="str">
-        <v>AP0066</v>
+        <v>AP0070</v>
       </c>
       <c r="D89" t="str">
-        <v>2020-05-04</v>
+        <v>2018-12-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -2443,7 +2443,7 @@
         <v>Allocated</v>
       </c>
       <c r="G89">
-        <v>46182</v>
+        <v>16275</v>
       </c>
     </row>
     <row r="90">
@@ -2451,13 +2451,13 @@
         <v>AST-1089</v>
       </c>
       <c r="B90" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C90" t="str">
-        <v>AP0066</v>
+        <v>AP0071</v>
       </c>
       <c r="D90" t="str">
-        <v>2020-05-04</v>
+        <v>2022-05-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -2466,7 +2466,7 @@
         <v>Allocated</v>
       </c>
       <c r="G90">
-        <v>56392</v>
+        <v>49020</v>
       </c>
     </row>
     <row r="91">
@@ -2477,10 +2477,10 @@
         <v>Laptop</v>
       </c>
       <c r="C91" t="str">
-        <v>AP0067</v>
+        <v>AP0072</v>
       </c>
       <c r="D91" t="str">
-        <v>2024-12-21</v>
+        <v>2023-09-12</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -2489,7 +2489,7 @@
         <v>Allocated</v>
       </c>
       <c r="G91">
-        <v>92186</v>
+        <v>100471</v>
       </c>
     </row>
     <row r="92">
@@ -2497,13 +2497,13 @@
         <v>AST-1091</v>
       </c>
       <c r="B92" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C92" t="str">
-        <v>AP0067</v>
+        <v>AP0073</v>
       </c>
       <c r="D92" t="str">
-        <v>2024-12-21</v>
+        <v>2022-02-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -2512,7 +2512,7 @@
         <v>Allocated</v>
       </c>
       <c r="G92">
-        <v>39337</v>
+        <v>52611</v>
       </c>
     </row>
     <row r="93">
@@ -2523,10 +2523,10 @@
         <v>Laptop</v>
       </c>
       <c r="C93" t="str">
-        <v>AP0068</v>
+        <v>AP0074</v>
       </c>
       <c r="D93" t="str">
-        <v>2023-07-19</v>
+        <v>2024-05-01</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>Allocated</v>
       </c>
       <c r="G93">
-        <v>92365</v>
+        <v>64627</v>
       </c>
     </row>
     <row r="94">
@@ -2543,13 +2543,13 @@
         <v>AST-1093</v>
       </c>
       <c r="B94" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C94" t="str">
-        <v>AP0070</v>
+        <v>AP0074</v>
       </c>
       <c r="D94" t="str">
-        <v>2018-12-17</v>
+        <v>2024-05-01</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -2558,7 +2558,7 @@
         <v>Allocated</v>
       </c>
       <c r="G94">
-        <v>105049</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="95">
@@ -2566,13 +2566,13 @@
         <v>AST-1094</v>
       </c>
       <c r="B95" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C95" t="str">
-        <v>AP0070</v>
+        <v>AP0075</v>
       </c>
       <c r="D95" t="str">
-        <v>2018-12-17</v>
+        <v>2017-01-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -2581,7 +2581,7 @@
         <v>Allocated</v>
       </c>
       <c r="G95">
-        <v>10163</v>
+        <v>86515</v>
       </c>
     </row>
     <row r="96">
@@ -2592,10 +2592,10 @@
         <v>Laptop</v>
       </c>
       <c r="C96" t="str">
-        <v>AP0072</v>
+        <v>AP0076</v>
       </c>
       <c r="D96" t="str">
-        <v>2023-09-12</v>
+        <v>2024-01-22</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -2604,7 +2604,7 @@
         <v>Allocated</v>
       </c>
       <c r="G96">
-        <v>106990</v>
+        <v>53352</v>
       </c>
     </row>
     <row r="97">
@@ -2612,13 +2612,13 @@
         <v>AST-1096</v>
       </c>
       <c r="B97" t="str">
-        <v>Access Card</v>
+        <v>SIM</v>
       </c>
       <c r="C97" t="str">
-        <v>AP0072</v>
+        <v>AP0076</v>
       </c>
       <c r="D97" t="str">
-        <v>2023-09-12</v>
+        <v>2024-01-22</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -2627,7 +2627,7 @@
         <v>Allocated</v>
       </c>
       <c r="G97">
-        <v>23556</v>
+        <v>19791</v>
       </c>
     </row>
     <row r="98">
@@ -2638,10 +2638,10 @@
         <v>Laptop</v>
       </c>
       <c r="C98" t="str">
-        <v>AP0073</v>
+        <v>AP0077</v>
       </c>
       <c r="D98" t="str">
-        <v>2022-02-10</v>
+        <v>2023-05-05</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -2650,7 +2650,7 @@
         <v>Allocated</v>
       </c>
       <c r="G98">
-        <v>60444</v>
+        <v>69702</v>
       </c>
     </row>
     <row r="99">
@@ -2661,10 +2661,10 @@
         <v>Laptop</v>
       </c>
       <c r="C99" t="str">
-        <v>AP0074</v>
+        <v>AP0078</v>
       </c>
       <c r="D99" t="str">
-        <v>2024-05-01</v>
+        <v>2023-04-07</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -2673,7 +2673,7 @@
         <v>Allocated</v>
       </c>
       <c r="G99">
-        <v>84997</v>
+        <v>46902</v>
       </c>
     </row>
     <row r="100">
@@ -2681,13 +2681,13 @@
         <v>AST-1099</v>
       </c>
       <c r="B100" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C100" t="str">
-        <v>AP0074</v>
+        <v>AP0079</v>
       </c>
       <c r="D100" t="str">
-        <v>2024-05-01</v>
+        <v>2019-10-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -2696,7 +2696,7 @@
         <v>Allocated</v>
       </c>
       <c r="G100">
-        <v>22042</v>
+        <v>105452</v>
       </c>
     </row>
     <row r="101">
@@ -2704,13 +2704,13 @@
         <v>AST-1100</v>
       </c>
       <c r="B101" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C101" t="str">
-        <v>AP0075</v>
+        <v>AP0079</v>
       </c>
       <c r="D101" t="str">
-        <v>2017-01-09</v>
+        <v>2019-10-19</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Allocated</v>
       </c>
       <c r="G101">
-        <v>63386</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="102">
@@ -2730,10 +2730,10 @@
         <v>Laptop</v>
       </c>
       <c r="C102" t="str">
-        <v>AP0077</v>
+        <v>AP0080</v>
       </c>
       <c r="D102" t="str">
-        <v>2023-05-05</v>
+        <v>2024-04-21</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -2742,7 +2742,7 @@
         <v>Allocated</v>
       </c>
       <c r="G102">
-        <v>71397</v>
+        <v>103572</v>
       </c>
     </row>
     <row r="103">
@@ -2750,13 +2750,13 @@
         <v>AST-1102</v>
       </c>
       <c r="B103" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C103" t="str">
-        <v>AP0077</v>
+        <v>AP0081</v>
       </c>
       <c r="D103" t="str">
-        <v>2023-05-05</v>
+        <v>2022-07-24</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -2765,7 +2765,7 @@
         <v>Allocated</v>
       </c>
       <c r="G103">
-        <v>43691</v>
+        <v>98525</v>
       </c>
     </row>
     <row r="104">
@@ -2776,10 +2776,10 @@
         <v>Laptop</v>
       </c>
       <c r="C104" t="str">
-        <v>AP0078</v>
+        <v>AP0082</v>
       </c>
       <c r="D104" t="str">
-        <v>2023-04-07</v>
+        <v>2021-06-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -2788,7 +2788,7 @@
         <v>Allocated</v>
       </c>
       <c r="G104">
-        <v>50111</v>
+        <v>106492</v>
       </c>
     </row>
     <row r="105">
@@ -2796,13 +2796,13 @@
         <v>AST-1104</v>
       </c>
       <c r="B105" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C105" t="str">
-        <v>AP0079</v>
+        <v>AP0082</v>
       </c>
       <c r="D105" t="str">
-        <v>2019-10-19</v>
+        <v>2021-06-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -2811,7 +2811,7 @@
         <v>Allocated</v>
       </c>
       <c r="G105">
-        <v>45648</v>
+        <v>37856</v>
       </c>
     </row>
     <row r="106">
@@ -2822,10 +2822,10 @@
         <v>Laptop</v>
       </c>
       <c r="C106" t="str">
-        <v>AP0080</v>
+        <v>AP0083</v>
       </c>
       <c r="D106" t="str">
-        <v>2024-04-21</v>
+        <v>2023-03-27</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -2834,7 +2834,7 @@
         <v>Allocated</v>
       </c>
       <c r="G106">
-        <v>84868</v>
+        <v>95288</v>
       </c>
     </row>
     <row r="107">
@@ -2845,10 +2845,10 @@
         <v>Laptop</v>
       </c>
       <c r="C107" t="str">
-        <v>AP0081</v>
+        <v>AP0084</v>
       </c>
       <c r="D107" t="str">
-        <v>2022-07-24</v>
+        <v>2017-09-26</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -2857,7 +2857,7 @@
         <v>Allocated</v>
       </c>
       <c r="G107">
-        <v>54387</v>
+        <v>55281</v>
       </c>
     </row>
     <row r="108">
@@ -2868,10 +2868,10 @@
         <v>Phone</v>
       </c>
       <c r="C108" t="str">
-        <v>AP0081</v>
+        <v>AP0084</v>
       </c>
       <c r="D108" t="str">
-        <v>2022-07-24</v>
+        <v>2017-09-26</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -2880,7 +2880,7 @@
         <v>Allocated</v>
       </c>
       <c r="G108">
-        <v>36174</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="109">
@@ -2891,10 +2891,10 @@
         <v>Laptop</v>
       </c>
       <c r="C109" t="str">
-        <v>AP0082</v>
+        <v>AP0085</v>
       </c>
       <c r="D109" t="str">
-        <v>2021-06-23</v>
+        <v>2020-09-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -2903,7 +2903,7 @@
         <v>Allocated</v>
       </c>
       <c r="G109">
-        <v>104307</v>
+        <v>60178</v>
       </c>
     </row>
     <row r="110">
@@ -2911,13 +2911,13 @@
         <v>AST-1109</v>
       </c>
       <c r="B110" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C110" t="str">
-        <v>AP0083</v>
+        <v>AP0085</v>
       </c>
       <c r="D110" t="str">
-        <v>2023-03-27</v>
+        <v>2020-09-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -2926,7 +2926,7 @@
         <v>Allocated</v>
       </c>
       <c r="G110">
-        <v>101646</v>
+        <v>56382</v>
       </c>
     </row>
     <row r="111">
@@ -2934,13 +2934,13 @@
         <v>AST-1110</v>
       </c>
       <c r="B111" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C111" t="str">
-        <v>AP0083</v>
+        <v>AP0086</v>
       </c>
       <c r="D111" t="str">
-        <v>2023-03-27</v>
+        <v>2020-12-22</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -2949,7 +2949,7 @@
         <v>Allocated</v>
       </c>
       <c r="G111">
-        <v>45892</v>
+        <v>53392</v>
       </c>
     </row>
     <row r="112">
@@ -2960,10 +2960,10 @@
         <v>Laptop</v>
       </c>
       <c r="C112" t="str">
-        <v>AP0084</v>
+        <v>AP0088</v>
       </c>
       <c r="D112" t="str">
-        <v>2017-09-26</v>
+        <v>2019-01-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -2972,7 +2972,7 @@
         <v>Allocated</v>
       </c>
       <c r="G112">
-        <v>53074</v>
+        <v>61022</v>
       </c>
     </row>
     <row r="113">
@@ -2980,13 +2980,13 @@
         <v>AST-1112</v>
       </c>
       <c r="B113" t="str">
-        <v>Access Card</v>
+        <v>Phone</v>
       </c>
       <c r="C113" t="str">
-        <v>AP0084</v>
+        <v>AP0088</v>
       </c>
       <c r="D113" t="str">
-        <v>2017-09-26</v>
+        <v>2019-01-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -2995,7 +2995,7 @@
         <v>Allocated</v>
       </c>
       <c r="G113">
-        <v>46165</v>
+        <v>14881</v>
       </c>
     </row>
     <row r="114">
@@ -3006,10 +3006,10 @@
         <v>Laptop</v>
       </c>
       <c r="C114" t="str">
-        <v>AP0085</v>
+        <v>AP0089</v>
       </c>
       <c r="D114" t="str">
-        <v>2020-09-23</v>
+        <v>2023-03-01</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -3018,7 +3018,7 @@
         <v>Allocated</v>
       </c>
       <c r="G114">
-        <v>68684</v>
+        <v>106698</v>
       </c>
     </row>
     <row r="115">
@@ -3026,13 +3026,13 @@
         <v>AST-1114</v>
       </c>
       <c r="B115" t="str">
-        <v>SIM</v>
+        <v>Access Card</v>
       </c>
       <c r="C115" t="str">
-        <v>AP0085</v>
+        <v>AP0089</v>
       </c>
       <c r="D115" t="str">
-        <v>2020-09-23</v>
+        <v>2023-03-01</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -3041,7 +3041,7 @@
         <v>Allocated</v>
       </c>
       <c r="G115">
-        <v>16700</v>
+        <v>51043</v>
       </c>
     </row>
     <row r="116">
@@ -3052,10 +3052,10 @@
         <v>Laptop</v>
       </c>
       <c r="C116" t="str">
-        <v>AP0086</v>
+        <v>AP0090</v>
       </c>
       <c r="D116" t="str">
-        <v>2020-12-22</v>
+        <v>2020-02-04</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -3064,7 +3064,7 @@
         <v>Allocated</v>
       </c>
       <c r="G116">
-        <v>58189</v>
+        <v>47232</v>
       </c>
     </row>
     <row r="117">
@@ -3072,13 +3072,13 @@
         <v>AST-1116</v>
       </c>
       <c r="B117" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C117" t="str">
-        <v>AP0088</v>
+        <v>AP0090</v>
       </c>
       <c r="D117" t="str">
-        <v>2019-01-23</v>
+        <v>2020-02-04</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -3087,7 +3087,7 @@
         <v>Allocated</v>
       </c>
       <c r="G117">
-        <v>62056</v>
+        <v>26802</v>
       </c>
     </row>
     <row r="118">
@@ -3098,10 +3098,10 @@
         <v>Laptop</v>
       </c>
       <c r="C118" t="str">
-        <v>AP0089</v>
+        <v>AP0091</v>
       </c>
       <c r="D118" t="str">
-        <v>2023-03-01</v>
+        <v>2020-01-26</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -3110,7 +3110,7 @@
         <v>Allocated</v>
       </c>
       <c r="G118">
-        <v>105864</v>
+        <v>64087</v>
       </c>
     </row>
     <row r="119">
@@ -3118,13 +3118,13 @@
         <v>AST-1118</v>
       </c>
       <c r="B119" t="str">
-        <v>Phone</v>
+        <v>SIM</v>
       </c>
       <c r="C119" t="str">
-        <v>AP0089</v>
+        <v>AP0091</v>
       </c>
       <c r="D119" t="str">
-        <v>2023-03-01</v>
+        <v>2020-01-26</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -3133,7 +3133,7 @@
         <v>Allocated</v>
       </c>
       <c r="G119">
-        <v>35725</v>
+        <v>53865</v>
       </c>
     </row>
     <row r="120">
@@ -3144,10 +3144,10 @@
         <v>Laptop</v>
       </c>
       <c r="C120" t="str">
-        <v>AP0090</v>
+        <v>AP0092</v>
       </c>
       <c r="D120" t="str">
-        <v>2020-02-04</v>
+        <v>2022-04-20</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -3156,7 +3156,7 @@
         <v>Allocated</v>
       </c>
       <c r="G120">
-        <v>79716</v>
+        <v>99889</v>
       </c>
     </row>
     <row r="121">
@@ -3164,13 +3164,13 @@
         <v>AST-1120</v>
       </c>
       <c r="B121" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C121" t="str">
-        <v>AP0091</v>
+        <v>AP0092</v>
       </c>
       <c r="D121" t="str">
-        <v>2020-01-26</v>
+        <v>2022-04-20</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -3179,7 +3179,7 @@
         <v>Allocated</v>
       </c>
       <c r="G121">
-        <v>52701</v>
+        <v>14101</v>
       </c>
     </row>
     <row r="122">
@@ -3190,10 +3190,10 @@
         <v>Laptop</v>
       </c>
       <c r="C122" t="str">
-        <v>AP0092</v>
+        <v>AP0093</v>
       </c>
       <c r="D122" t="str">
-        <v>2022-04-20</v>
+        <v>2018-02-04</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -3202,7 +3202,7 @@
         <v>Allocated</v>
       </c>
       <c r="G122">
-        <v>101468</v>
+        <v>101879</v>
       </c>
     </row>
     <row r="123">
@@ -3213,10 +3213,10 @@
         <v>Laptop</v>
       </c>
       <c r="C123" t="str">
-        <v>AP0093</v>
+        <v>AP0095</v>
       </c>
       <c r="D123" t="str">
-        <v>2018-02-04</v>
+        <v>2019-03-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -3225,7 +3225,7 @@
         <v>Allocated</v>
       </c>
       <c r="G123">
-        <v>59461</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="124">
@@ -3233,7 +3233,7 @@
         <v>AST-1123</v>
       </c>
       <c r="B124" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C124" t="str">
         <v>AP0095</v>
@@ -3248,7 +3248,7 @@
         <v>Allocated</v>
       </c>
       <c r="G124">
-        <v>52826</v>
+        <v>56392</v>
       </c>
     </row>
     <row r="125">
@@ -3256,13 +3256,13 @@
         <v>AST-1124</v>
       </c>
       <c r="B125" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C125" t="str">
-        <v>AP0095</v>
+        <v>AP0096</v>
       </c>
       <c r="D125" t="str">
-        <v>2019-03-16</v>
+        <v>2023-04-11</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -3271,7 +3271,7 @@
         <v>Allocated</v>
       </c>
       <c r="G125">
-        <v>8471</v>
+        <v>92186</v>
       </c>
     </row>
     <row r="126">
@@ -3279,7 +3279,7 @@
         <v>AST-1125</v>
       </c>
       <c r="B126" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C126" t="str">
         <v>AP0096</v>
@@ -3294,7 +3294,7 @@
         <v>Allocated</v>
       </c>
       <c r="G126">
-        <v>51773</v>
+        <v>39337</v>
       </c>
     </row>
     <row r="127">
@@ -3302,13 +3302,13 @@
         <v>AST-1126</v>
       </c>
       <c r="B127" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C127" t="str">
-        <v>AP0096</v>
+        <v>AP0097</v>
       </c>
       <c r="D127" t="str">
-        <v>2023-04-11</v>
+        <v>2019-03-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -3317,7 +3317,7 @@
         <v>Allocated</v>
       </c>
       <c r="G127">
-        <v>58037</v>
+        <v>92365</v>
       </c>
     </row>
     <row r="128">
@@ -3328,10 +3328,10 @@
         <v>Laptop</v>
       </c>
       <c r="C128" t="str">
-        <v>AP0097</v>
+        <v>AP0100</v>
       </c>
       <c r="D128" t="str">
-        <v>2019-03-02</v>
+        <v>2019-02-19</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -3340,7 +3340,7 @@
         <v>Allocated</v>
       </c>
       <c r="G128">
-        <v>102484</v>
+        <v>105049</v>
       </c>
     </row>
     <row r="129">
@@ -3348,13 +3348,13 @@
         <v>AST-1128</v>
       </c>
       <c r="B129" t="str">
-        <v>Phone</v>
+        <v>SIM</v>
       </c>
       <c r="C129" t="str">
-        <v>AP0097</v>
+        <v>AP0100</v>
       </c>
       <c r="D129" t="str">
-        <v>2019-03-02</v>
+        <v>2019-02-19</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -3363,7 +3363,7 @@
         <v>Allocated</v>
       </c>
       <c r="G129">
-        <v>21845</v>
+        <v>10163</v>
       </c>
     </row>
     <row r="130">
@@ -3374,10 +3374,10 @@
         <v>Laptop</v>
       </c>
       <c r="C130" t="str">
-        <v>AP0098</v>
+        <v>AP0102</v>
       </c>
       <c r="D130" t="str">
-        <v>2021-03-03</v>
+        <v>2024-03-17</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -3386,7 +3386,7 @@
         <v>Allocated</v>
       </c>
       <c r="G130">
-        <v>60853</v>
+        <v>106990</v>
       </c>
     </row>
     <row r="131">
@@ -3394,13 +3394,13 @@
         <v>AST-1130</v>
       </c>
       <c r="B131" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C131" t="str">
-        <v>AP0100</v>
+        <v>AP0102</v>
       </c>
       <c r="D131" t="str">
-        <v>2019-02-19</v>
+        <v>2024-03-17</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>Allocated</v>
       </c>
       <c r="G131">
-        <v>105503</v>
+        <v>23556</v>
       </c>
     </row>
     <row r="132">
@@ -3420,10 +3420,10 @@
         <v>Laptop</v>
       </c>
       <c r="C132" t="str">
-        <v>AP0101</v>
+        <v>AP0103</v>
       </c>
       <c r="D132" t="str">
-        <v>2019-01-11</v>
+        <v>2019-07-10</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -3432,7 +3432,7 @@
         <v>Allocated</v>
       </c>
       <c r="G132">
-        <v>62315</v>
+        <v>60444</v>
       </c>
     </row>
     <row r="133">
@@ -3443,10 +3443,10 @@
         <v>Laptop</v>
       </c>
       <c r="C133" t="str">
-        <v>AP0102</v>
+        <v>AP0104</v>
       </c>
       <c r="D133" t="str">
-        <v>2024-03-17</v>
+        <v>2024-10-27</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -3455,7 +3455,7 @@
         <v>Allocated</v>
       </c>
       <c r="G133">
-        <v>105531</v>
+        <v>84997</v>
       </c>
     </row>
     <row r="134">
@@ -3463,7 +3463,7 @@
         <v>AST-1133</v>
       </c>
       <c r="B134" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C134" t="str">
         <v>AP0104</v>
@@ -3478,7 +3478,7 @@
         <v>Allocated</v>
       </c>
       <c r="G134">
-        <v>49420</v>
+        <v>22042</v>
       </c>
     </row>
     <row r="135">
@@ -3501,7 +3501,7 @@
         <v>Allocated</v>
       </c>
       <c r="G135">
-        <v>73688</v>
+        <v>63386</v>
       </c>
     </row>
     <row r="136">
@@ -3512,10 +3512,10 @@
         <v>Laptop</v>
       </c>
       <c r="C136" t="str">
-        <v>AP0106</v>
+        <v>AP0107</v>
       </c>
       <c r="D136" t="str">
-        <v>2024-08-06</v>
+        <v>2023-02-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -3524,7 +3524,7 @@
         <v>Allocated</v>
       </c>
       <c r="G136">
-        <v>107975</v>
+        <v>71397</v>
       </c>
     </row>
     <row r="137">
@@ -3532,7 +3532,7 @@
         <v>AST-1136</v>
       </c>
       <c r="B137" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C137" t="str">
         <v>AP0107</v>
@@ -3547,7 +3547,7 @@
         <v>Allocated</v>
       </c>
       <c r="G137">
-        <v>100826</v>
+        <v>43691</v>
       </c>
     </row>
     <row r="138">
@@ -3555,13 +3555,13 @@
         <v>AST-1137</v>
       </c>
       <c r="B138" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C138" t="str">
-        <v>AP0107</v>
+        <v>AP0108</v>
       </c>
       <c r="D138" t="str">
-        <v>2023-02-16</v>
+        <v>2019-02-20</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
         <v>Allocated</v>
       </c>
       <c r="G138">
-        <v>54611</v>
+        <v>50111</v>
       </c>
     </row>
     <row r="139">
@@ -3581,10 +3581,10 @@
         <v>Laptop</v>
       </c>
       <c r="C139" t="str">
-        <v>AP0108</v>
+        <v>AP0109</v>
       </c>
       <c r="D139" t="str">
-        <v>2019-02-20</v>
+        <v>2023-09-24</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allocated</v>
       </c>
       <c r="G139">
-        <v>89506</v>
+        <v>45648</v>
       </c>
     </row>
     <row r="140">
@@ -3601,13 +3601,13 @@
         <v>AST-1139</v>
       </c>
       <c r="B140" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C140" t="str">
-        <v>AP0108</v>
+        <v>AP0110</v>
       </c>
       <c r="D140" t="str">
-        <v>2019-02-20</v>
+        <v>2020-07-27</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -3616,7 +3616,7 @@
         <v>Allocated</v>
       </c>
       <c r="G140">
-        <v>25948</v>
+        <v>84868</v>
       </c>
     </row>
     <row r="141">
@@ -3627,10 +3627,10 @@
         <v>Laptop</v>
       </c>
       <c r="C141" t="str">
-        <v>AP0109</v>
+        <v>AP0111</v>
       </c>
       <c r="D141" t="str">
-        <v>2023-09-24</v>
+        <v>2022-09-26</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -3639,7 +3639,7 @@
         <v>Allocated</v>
       </c>
       <c r="G141">
-        <v>100693</v>
+        <v>54387</v>
       </c>
     </row>
     <row r="142">
@@ -3647,13 +3647,13 @@
         <v>AST-1141</v>
       </c>
       <c r="B142" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C142" t="str">
-        <v>AP0110</v>
+        <v>AP0111</v>
       </c>
       <c r="D142" t="str">
-        <v>2020-07-27</v>
+        <v>2022-09-26</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -3662,7 +3662,7 @@
         <v>Allocated</v>
       </c>
       <c r="G142">
-        <v>75681</v>
+        <v>36174</v>
       </c>
     </row>
     <row r="143">
@@ -3673,10 +3673,10 @@
         <v>Laptop</v>
       </c>
       <c r="C143" t="str">
-        <v>AP0111</v>
+        <v>AP0112</v>
       </c>
       <c r="D143" t="str">
-        <v>2022-09-26</v>
+        <v>2021-11-08</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -3685,7 +3685,7 @@
         <v>Allocated</v>
       </c>
       <c r="G143">
-        <v>105587</v>
+        <v>104307</v>
       </c>
     </row>
     <row r="144">
@@ -3696,10 +3696,10 @@
         <v>Laptop</v>
       </c>
       <c r="C144" t="str">
-        <v>AP0112</v>
+        <v>AP0113</v>
       </c>
       <c r="D144" t="str">
-        <v>2021-11-08</v>
+        <v>2021-07-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -3708,7 +3708,7 @@
         <v>Allocated</v>
       </c>
       <c r="G144">
-        <v>88410</v>
+        <v>101646</v>
       </c>
     </row>
     <row r="145">
@@ -3716,7 +3716,7 @@
         <v>AST-1144</v>
       </c>
       <c r="B145" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C145" t="str">
         <v>AP0113</v>
@@ -3731,7 +3731,7 @@
         <v>Allocated</v>
       </c>
       <c r="G145">
-        <v>104283</v>
+        <v>45892</v>
       </c>
     </row>
     <row r="146">
@@ -3739,13 +3739,13 @@
         <v>AST-1145</v>
       </c>
       <c r="B146" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C146" t="str">
-        <v>AP0113</v>
+        <v>AP0114</v>
       </c>
       <c r="D146" t="str">
-        <v>2021-07-16</v>
+        <v>2017-02-19</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -3754,7 +3754,7 @@
         <v>Allocated</v>
       </c>
       <c r="G146">
-        <v>43377</v>
+        <v>53074</v>
       </c>
     </row>
     <row r="147">
@@ -3762,7 +3762,7 @@
         <v>AST-1146</v>
       </c>
       <c r="B147" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C147" t="str">
         <v>AP0114</v>
@@ -3777,7 +3777,7 @@
         <v>Allocated</v>
       </c>
       <c r="G147">
-        <v>54532</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="148">
@@ -3800,7 +3800,7 @@
         <v>Allocated</v>
       </c>
       <c r="G148">
-        <v>88965</v>
+        <v>68684</v>
       </c>
     </row>
     <row r="149">
@@ -3808,7 +3808,7 @@
         <v>AST-1148</v>
       </c>
       <c r="B149" t="str">
-        <v>Access Card</v>
+        <v>SIM</v>
       </c>
       <c r="C149" t="str">
         <v>AP0115</v>
@@ -3823,7 +3823,7 @@
         <v>Allocated</v>
       </c>
       <c r="G149">
-        <v>20027</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="150">
@@ -3846,7 +3846,7 @@
         <v>Allocated</v>
       </c>
       <c r="G150">
-        <v>98581</v>
+        <v>58189</v>
       </c>
     </row>
     <row r="151">
@@ -3854,13 +3854,13 @@
         <v>AST-1150</v>
       </c>
       <c r="B151" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C151" t="str">
-        <v>AP0116</v>
+        <v>AP0117</v>
       </c>
       <c r="D151" t="str">
-        <v>2020-02-01</v>
+        <v>2020-03-08</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -3869,7 +3869,7 @@
         <v>Allocated</v>
       </c>
       <c r="G151">
-        <v>36644</v>
+        <v>62056</v>
       </c>
     </row>
     <row r="152">
@@ -3880,10 +3880,10 @@
         <v>Laptop</v>
       </c>
       <c r="C152" t="str">
-        <v>AP0117</v>
+        <v>AP0118</v>
       </c>
       <c r="D152" t="str">
-        <v>2020-03-08</v>
+        <v>2024-08-25</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -3892,7 +3892,7 @@
         <v>Allocated</v>
       </c>
       <c r="G152">
-        <v>46836</v>
+        <v>105864</v>
       </c>
     </row>
     <row r="153">
@@ -3900,7 +3900,7 @@
         <v>AST-1152</v>
       </c>
       <c r="B153" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C153" t="str">
         <v>AP0118</v>
@@ -3915,7 +3915,7 @@
         <v>Allocated</v>
       </c>
       <c r="G153">
-        <v>85467</v>
+        <v>35725</v>
       </c>
     </row>
     <row r="154">
@@ -3938,7 +3938,7 @@
         <v>Allocated</v>
       </c>
       <c r="G154">
-        <v>65433</v>
+        <v>79716</v>
       </c>
     </row>
     <row r="155">
@@ -3946,13 +3946,13 @@
         <v>AST-1154</v>
       </c>
       <c r="B155" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C155" t="str">
-        <v>AP0119</v>
+        <v>AP0120</v>
       </c>
       <c r="D155" t="str">
-        <v>2021-07-04</v>
+        <v>2018-04-19</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -3961,7 +3961,7 @@
         <v>Allocated</v>
       </c>
       <c r="G155">
-        <v>8855</v>
+        <v>52701</v>
       </c>
     </row>
     <row r="156">
@@ -3972,10 +3972,10 @@
         <v>Laptop</v>
       </c>
       <c r="C156" t="str">
-        <v>AP0120</v>
+        <v>AP0121</v>
       </c>
       <c r="D156" t="str">
-        <v>2018-04-19</v>
+        <v>2023-09-22</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -3984,7 +3984,7 @@
         <v>Allocated</v>
       </c>
       <c r="G156">
-        <v>89925</v>
+        <v>101468</v>
       </c>
     </row>
     <row r="157">
@@ -3992,13 +3992,13 @@
         <v>AST-1156</v>
       </c>
       <c r="B157" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C157" t="str">
-        <v>AP0120</v>
+        <v>AP0122</v>
       </c>
       <c r="D157" t="str">
-        <v>2018-04-19</v>
+        <v>2022-05-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -4007,7 +4007,7 @@
         <v>Allocated</v>
       </c>
       <c r="G157">
-        <v>38446</v>
+        <v>59461</v>
       </c>
     </row>
     <row r="158">
@@ -4018,10 +4018,10 @@
         <v>Laptop</v>
       </c>
       <c r="C158" t="str">
-        <v>AP0121</v>
+        <v>AP0123</v>
       </c>
       <c r="D158" t="str">
-        <v>2023-09-22</v>
+        <v>2017-10-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>Allocated</v>
       </c>
       <c r="G158">
-        <v>50132</v>
+        <v>52826</v>
       </c>
     </row>
     <row r="159">
@@ -4038,13 +4038,13 @@
         <v>AST-1158</v>
       </c>
       <c r="B159" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C159" t="str">
-        <v>AP0122</v>
+        <v>AP0123</v>
       </c>
       <c r="D159" t="str">
-        <v>2022-05-23</v>
+        <v>2017-10-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -4053,7 +4053,7 @@
         <v>Allocated</v>
       </c>
       <c r="G159">
-        <v>86268</v>
+        <v>8471</v>
       </c>
     </row>
     <row r="160">
@@ -4061,13 +4061,13 @@
         <v>AST-1159</v>
       </c>
       <c r="B160" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C160" t="str">
-        <v>AP0122</v>
+        <v>AP0124</v>
       </c>
       <c r="D160" t="str">
-        <v>2022-05-23</v>
+        <v>2024-06-21</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -4076,7 +4076,7 @@
         <v>Allocated</v>
       </c>
       <c r="G160">
-        <v>36243</v>
+        <v>51773</v>
       </c>
     </row>
     <row r="161">
@@ -4084,13 +4084,13 @@
         <v>AST-1160</v>
       </c>
       <c r="B161" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C161" t="str">
-        <v>AP0123</v>
+        <v>AP0124</v>
       </c>
       <c r="D161" t="str">
-        <v>2017-10-16</v>
+        <v>2024-06-21</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -4099,7 +4099,7 @@
         <v>Allocated</v>
       </c>
       <c r="G161">
-        <v>54512</v>
+        <v>58037</v>
       </c>
     </row>
     <row r="162">
@@ -4110,10 +4110,10 @@
         <v>Laptop</v>
       </c>
       <c r="C162" t="str">
-        <v>AP0124</v>
+        <v>AP0125</v>
       </c>
       <c r="D162" t="str">
-        <v>2024-06-21</v>
+        <v>2019-09-21</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -4122,7 +4122,7 @@
         <v>Allocated</v>
       </c>
       <c r="G162">
-        <v>98142</v>
+        <v>102484</v>
       </c>
     </row>
     <row r="163">
@@ -4130,7 +4130,7 @@
         <v>AST-1162</v>
       </c>
       <c r="B163" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C163" t="str">
         <v>AP0125</v>
@@ -4145,7 +4145,7 @@
         <v>Allocated</v>
       </c>
       <c r="G163">
-        <v>76128</v>
+        <v>21845</v>
       </c>
     </row>
     <row r="164">
@@ -4168,7 +4168,7 @@
         <v>Allocated</v>
       </c>
       <c r="G164">
-        <v>77797</v>
+        <v>60853</v>
       </c>
     </row>
     <row r="165">
@@ -4176,13 +4176,13 @@
         <v>AST-1164</v>
       </c>
       <c r="B165" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C165" t="str">
-        <v>AP0128</v>
+        <v>AP0129</v>
       </c>
       <c r="D165" t="str">
-        <v>2023-04-12</v>
+        <v>2022-05-06</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -4191,7 +4191,7 @@
         <v>Allocated</v>
       </c>
       <c r="G165">
-        <v>30315</v>
+        <v>105503</v>
       </c>
     </row>
     <row r="166">
@@ -4202,10 +4202,10 @@
         <v>Laptop</v>
       </c>
       <c r="C166" t="str">
-        <v>AP0129</v>
+        <v>AP0130</v>
       </c>
       <c r="D166" t="str">
-        <v>2022-05-06</v>
+        <v>2021-03-06</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -4214,7 +4214,7 @@
         <v>Allocated</v>
       </c>
       <c r="G166">
-        <v>104168</v>
+        <v>62315</v>
       </c>
     </row>
     <row r="167">
@@ -4225,10 +4225,10 @@
         <v>Laptop</v>
       </c>
       <c r="C167" t="str">
-        <v>AP0130</v>
+        <v>AP0131</v>
       </c>
       <c r="D167" t="str">
-        <v>2021-03-06</v>
+        <v>2021-04-24</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -4237,7 +4237,7 @@
         <v>Allocated</v>
       </c>
       <c r="G167">
-        <v>74994</v>
+        <v>105531</v>
       </c>
     </row>
     <row r="168">
@@ -4248,10 +4248,10 @@
         <v>Laptop</v>
       </c>
       <c r="C168" t="str">
-        <v>AP0131</v>
+        <v>AP0134</v>
       </c>
       <c r="D168" t="str">
-        <v>2021-04-24</v>
+        <v>2019-11-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -4260,7 +4260,7 @@
         <v>Allocated</v>
       </c>
       <c r="G168">
-        <v>52473</v>
+        <v>49420</v>
       </c>
     </row>
     <row r="169">
@@ -4271,10 +4271,10 @@
         <v>Laptop</v>
       </c>
       <c r="C169" t="str">
-        <v>AP0132</v>
+        <v>AP0135</v>
       </c>
       <c r="D169" t="str">
-        <v>2019-07-01</v>
+        <v>2021-02-07</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>Allocated</v>
       </c>
       <c r="G169">
-        <v>108940</v>
+        <v>73688</v>
       </c>
     </row>
     <row r="170">
@@ -4294,10 +4294,10 @@
         <v>Laptop</v>
       </c>
       <c r="C170" t="str">
-        <v>AP0134</v>
+        <v>AP0136</v>
       </c>
       <c r="D170" t="str">
-        <v>2019-11-02</v>
+        <v>2017-08-26</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -4306,7 +4306,7 @@
         <v>Allocated</v>
       </c>
       <c r="G170">
-        <v>58774</v>
+        <v>107975</v>
       </c>
     </row>
     <row r="171">
@@ -4317,10 +4317,10 @@
         <v>Laptop</v>
       </c>
       <c r="C171" t="str">
-        <v>AP0135</v>
+        <v>AP0137</v>
       </c>
       <c r="D171" t="str">
-        <v>2021-02-07</v>
+        <v>2019-03-13</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -4329,7 +4329,7 @@
         <v>Allocated</v>
       </c>
       <c r="G171">
-        <v>73990</v>
+        <v>100826</v>
       </c>
     </row>
     <row r="172">
@@ -4337,13 +4337,13 @@
         <v>AST-1171</v>
       </c>
       <c r="B172" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C172" t="str">
-        <v>AP0136</v>
+        <v>AP0137</v>
       </c>
       <c r="D172" t="str">
-        <v>2017-08-26</v>
+        <v>2019-03-13</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -4352,7 +4352,7 @@
         <v>Allocated</v>
       </c>
       <c r="G172">
-        <v>88585</v>
+        <v>54611</v>
       </c>
     </row>
     <row r="173">
@@ -4360,13 +4360,13 @@
         <v>AST-1172</v>
       </c>
       <c r="B173" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C173" t="str">
-        <v>AP0136</v>
+        <v>AP0138</v>
       </c>
       <c r="D173" t="str">
-        <v>2017-08-26</v>
+        <v>2022-07-09</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -4375,7 +4375,7 @@
         <v>Allocated</v>
       </c>
       <c r="G173">
-        <v>54723</v>
+        <v>89506</v>
       </c>
     </row>
     <row r="174">
@@ -4383,13 +4383,13 @@
         <v>AST-1173</v>
       </c>
       <c r="B174" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C174" t="str">
-        <v>AP0137</v>
+        <v>AP0138</v>
       </c>
       <c r="D174" t="str">
-        <v>2019-03-13</v>
+        <v>2022-07-09</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -4398,7 +4398,7 @@
         <v>Allocated</v>
       </c>
       <c r="G174">
-        <v>46294</v>
+        <v>25948</v>
       </c>
     </row>
     <row r="175">
@@ -4409,10 +4409,10 @@
         <v>Laptop</v>
       </c>
       <c r="C175" t="str">
-        <v>AP0140</v>
+        <v>AP0139</v>
       </c>
       <c r="D175" t="str">
-        <v>2017-11-07</v>
+        <v>2022-06-26</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -4421,7 +4421,7 @@
         <v>Allocated</v>
       </c>
       <c r="G175">
-        <v>80434</v>
+        <v>100693</v>
       </c>
     </row>
     <row r="176">
@@ -4429,7 +4429,7 @@
         <v>AST-1175</v>
       </c>
       <c r="B176" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C176" t="str">
         <v>AP0140</v>
@@ -4444,7 +4444,7 @@
         <v>Allocated</v>
       </c>
       <c r="G176">
-        <v>55962</v>
+        <v>75681</v>
       </c>
     </row>
     <row r="177">
@@ -4467,7 +4467,7 @@
         <v>Allocated</v>
       </c>
       <c r="G177">
-        <v>65177</v>
+        <v>105587</v>
       </c>
     </row>
     <row r="178">
@@ -4475,13 +4475,13 @@
         <v>AST-1177</v>
       </c>
       <c r="B178" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C178" t="str">
-        <v>AP0141</v>
+        <v>AP0142</v>
       </c>
       <c r="D178" t="str">
-        <v>2022-12-12</v>
+        <v>2023-12-13</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -4490,7 +4490,7 @@
         <v>Allocated</v>
       </c>
       <c r="G178">
-        <v>7951</v>
+        <v>88410</v>
       </c>
     </row>
     <row r="179">
@@ -4501,10 +4501,10 @@
         <v>Laptop</v>
       </c>
       <c r="C179" t="str">
-        <v>AP0142</v>
+        <v>AP0143</v>
       </c>
       <c r="D179" t="str">
-        <v>2023-12-13</v>
+        <v>2021-08-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -4513,7 +4513,7 @@
         <v>Allocated</v>
       </c>
       <c r="G179">
-        <v>56730</v>
+        <v>104283</v>
       </c>
     </row>
     <row r="180">
@@ -4521,7 +4521,7 @@
         <v>AST-1179</v>
       </c>
       <c r="B180" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C180" t="str">
         <v>AP0143</v>
@@ -4536,7 +4536,7 @@
         <v>Allocated</v>
       </c>
       <c r="G180">
-        <v>53896</v>
+        <v>43377</v>
       </c>
     </row>
     <row r="181">
@@ -4559,7 +4559,7 @@
         <v>Allocated</v>
       </c>
       <c r="G181">
-        <v>78641</v>
+        <v>54532</v>
       </c>
     </row>
     <row r="182">
@@ -4582,7 +4582,7 @@
         <v>Allocated</v>
       </c>
       <c r="G182">
-        <v>99685</v>
+        <v>88965</v>
       </c>
     </row>
     <row r="183">
@@ -4590,13 +4590,13 @@
         <v>AST-1182</v>
       </c>
       <c r="B183" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C183" t="str">
-        <v>AP0146</v>
+        <v>AP0145</v>
       </c>
       <c r="D183" t="str">
-        <v>2021-01-23</v>
+        <v>2019-06-06</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -4605,7 +4605,7 @@
         <v>Allocated</v>
       </c>
       <c r="G183">
-        <v>107173</v>
+        <v>20027</v>
       </c>
     </row>
     <row r="184">
@@ -4613,7 +4613,7 @@
         <v>AST-1183</v>
       </c>
       <c r="B184" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C184" t="str">
         <v>AP0146</v>
@@ -4628,7 +4628,7 @@
         <v>Allocated</v>
       </c>
       <c r="G184">
-        <v>23947</v>
+        <v>98581</v>
       </c>
     </row>
     <row r="185">
@@ -4636,13 +4636,13 @@
         <v>AST-1184</v>
       </c>
       <c r="B185" t="str">
-        <v>Laptop</v>
+        <v>Access Card</v>
       </c>
       <c r="C185" t="str">
-        <v>AP0147</v>
+        <v>AP0146</v>
       </c>
       <c r="D185" t="str">
-        <v>2023-07-22</v>
+        <v>2021-01-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -4651,7 +4651,7 @@
         <v>Allocated</v>
       </c>
       <c r="G185">
-        <v>91514</v>
+        <v>36644</v>
       </c>
     </row>
     <row r="186">
@@ -4662,10 +4662,10 @@
         <v>Laptop</v>
       </c>
       <c r="C186" t="str">
-        <v>AP0148</v>
+        <v>AP0147</v>
       </c>
       <c r="D186" t="str">
-        <v>2021-06-02</v>
+        <v>2023-07-22</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -4674,7 +4674,7 @@
         <v>Allocated</v>
       </c>
       <c r="G186">
-        <v>64133</v>
+        <v>46836</v>
       </c>
     </row>
     <row r="187">
@@ -4682,7 +4682,7 @@
         <v>AST-1186</v>
       </c>
       <c r="B187" t="str">
-        <v>Phone</v>
+        <v>Laptop</v>
       </c>
       <c r="C187" t="str">
         <v>AP0148</v>
@@ -4697,7 +4697,7 @@
         <v>Allocated</v>
       </c>
       <c r="G187">
-        <v>7011</v>
+        <v>85467</v>
       </c>
     </row>
     <row r="188">
@@ -4705,7 +4705,7 @@
         <v>AST-1187</v>
       </c>
       <c r="B188" t="str">
-        <v>Laptop</v>
+        <v>Phone</v>
       </c>
       <c r="C188" t="str">
         <v/>
@@ -4720,7 +4720,7 @@
         <v>Lost</v>
       </c>
       <c r="G188">
-        <v>43180</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="189">
@@ -4728,7 +4728,7 @@
         <v>AST-1188</v>
       </c>
       <c r="B189" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C189" t="str">
         <v/>
@@ -4743,7 +4743,7 @@
         <v>Lost</v>
       </c>
       <c r="G189">
-        <v>37123</v>
+        <v>48478</v>
       </c>
     </row>
     <row r="190">
@@ -4751,7 +4751,7 @@
         <v>AST-1189</v>
       </c>
       <c r="B190" t="str">
-        <v>SIM</v>
+        <v>Laptop</v>
       </c>
       <c r="C190" t="str">
         <v/>
@@ -4766,7 +4766,7 @@
         <v>Lost</v>
       </c>
       <c r="G190">
-        <v>44398</v>
+        <v>74662</v>
       </c>
     </row>
     <row r="191">
@@ -4774,7 +4774,7 @@
         <v>AST-1190</v>
       </c>
       <c r="B191" t="str">
-        <v>Other</v>
+        <v>SIM</v>
       </c>
       <c r="C191" t="str">
         <v/>
@@ -4789,7 +4789,7 @@
         <v>In-stock</v>
       </c>
       <c r="G191">
-        <v>30775</v>
+        <v>44532</v>
       </c>
     </row>
     <row r="192">
@@ -4812,7 +4812,7 @@
         <v>In-stock</v>
       </c>
       <c r="G192">
-        <v>42864</v>
+        <v>63987</v>
       </c>
     </row>
     <row r="193">
@@ -4820,7 +4820,7 @@
         <v>AST-1192</v>
       </c>
       <c r="B193" t="str">
-        <v>Access Card</v>
+        <v>Laptop</v>
       </c>
       <c r="C193" t="str">
         <v/>
@@ -4835,7 +4835,7 @@
         <v>In-stock</v>
       </c>
       <c r="G193">
-        <v>20488</v>
+        <v>25526</v>
       </c>
     </row>
     <row r="194">
@@ -4843,7 +4843,7 @@
         <v>AST-1193</v>
       </c>
       <c r="B194" t="str">
-        <v>Laptop</v>
+        <v>SIM</v>
       </c>
       <c r="C194" t="str">
         <v/>
@@ -4858,7 +4858,7 @@
         <v>In-stock</v>
       </c>
       <c r="G194">
-        <v>60232</v>
+        <v>53788</v>
       </c>
     </row>
     <row r="195">
@@ -4866,7 +4866,7 @@
         <v>AST-1194</v>
       </c>
       <c r="B195" t="str">
-        <v>Phone</v>
+        <v>SIM</v>
       </c>
       <c r="C195" t="str">
         <v/>
@@ -4881,7 +4881,7 @@
         <v>In-stock</v>
       </c>
       <c r="G195">
-        <v>86328</v>
+        <v>45150</v>
       </c>
     </row>
     <row r="196">
@@ -4889,7 +4889,7 @@
         <v>AST-1195</v>
       </c>
       <c r="B196" t="str">
-        <v>Phone</v>
+        <v>Other</v>
       </c>
       <c r="C196" t="str">
         <v/>
@@ -4904,7 +4904,7 @@
         <v>In-stock</v>
       </c>
       <c r="G196">
-        <v>26036</v>
+        <v>61327</v>
       </c>
     </row>
     <row r="197">
@@ -4927,7 +4927,7 @@
         <v>In-stock</v>
       </c>
       <c r="G197">
-        <v>45566</v>
+        <v>30243</v>
       </c>
     </row>
     <row r="198">
@@ -4935,7 +4935,7 @@
         <v>AST-1197</v>
       </c>
       <c r="B198" t="str">
-        <v>Phone</v>
+        <v>Other</v>
       </c>
       <c r="C198" t="str">
         <v/>
@@ -4950,7 +4950,7 @@
         <v>In-stock</v>
       </c>
       <c r="G198">
-        <v>37515</v>
+        <v>45363</v>
       </c>
     </row>
   </sheetData>
